--- a/attention/mixed_quant_sparse_flash_mla/tests/pytest/excel/testcase.xlsx
+++ b/attention/mixed_quant_sparse_flash_mla/tests/pytest/excel/testcase.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AQ21"/>
+  <dimension ref="A1:AS22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -611,35 +611,45 @@
       </c>
       <c r="AK1" s="1" t="inlineStr">
         <is>
+          <t>ori_topk_length</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>cmp_topk_length</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
           <t>seqused_q</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
+      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>cu_seqlens_q</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="AO1" s="1" t="inlineStr">
         <is>
           <t>seqused_ori_kv</t>
         </is>
       </c>
-      <c r="AN1" s="1" t="inlineStr">
+      <c r="AP1" s="1" t="inlineStr">
         <is>
           <t>seqused_cmp_kv</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
+      <c r="AQ1" s="1" t="inlineStr">
         <is>
           <t>cu_seqlens_ori_kv</t>
         </is>
       </c>
-      <c r="AP1" s="1" t="inlineStr">
+      <c r="AR1" s="1" t="inlineStr">
         <is>
           <t>cu_seqlens_cmp_kv</t>
         </is>
       </c>
-      <c r="AQ1" s="1" t="inlineStr">
+      <c r="AS1" s="1" t="inlineStr">
         <is>
           <t>cmp_residual_kv</t>
         </is>
@@ -773,6 +783,8 @@
       <c r="AO2" t="inlineStr"/>
       <c r="AP2" t="inlineStr"/>
       <c r="AQ2" t="inlineStr"/>
+      <c r="AR2" t="inlineStr"/>
+      <c r="AS2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr"/>
@@ -902,6 +914,8 @@
       <c r="AO3" t="inlineStr"/>
       <c r="AP3" t="inlineStr"/>
       <c r="AQ3" t="inlineStr"/>
+      <c r="AR3" t="inlineStr"/>
+      <c r="AS3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr"/>
@@ -1031,6 +1045,8 @@
       <c r="AO4" t="inlineStr"/>
       <c r="AP4" t="inlineStr"/>
       <c r="AQ4" t="inlineStr"/>
+      <c r="AR4" t="inlineStr"/>
+      <c r="AS4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr"/>
@@ -1160,6 +1176,8 @@
       <c r="AO5" t="inlineStr"/>
       <c r="AP5" t="inlineStr"/>
       <c r="AQ5" t="inlineStr"/>
+      <c r="AR5" t="inlineStr"/>
+      <c r="AS5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
@@ -1289,6 +1307,8 @@
       <c r="AO6" t="inlineStr"/>
       <c r="AP6" t="inlineStr"/>
       <c r="AQ6" t="inlineStr"/>
+      <c r="AR6" t="inlineStr"/>
+      <c r="AS6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr"/>
@@ -1418,6 +1438,8 @@
       <c r="AO7" t="inlineStr"/>
       <c r="AP7" t="inlineStr"/>
       <c r="AQ7" t="inlineStr"/>
+      <c r="AR7" t="inlineStr"/>
+      <c r="AS7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr"/>
@@ -1547,6 +1569,8 @@
       <c r="AO8" t="inlineStr"/>
       <c r="AP8" t="inlineStr"/>
       <c r="AQ8" t="inlineStr"/>
+      <c r="AR8" t="inlineStr"/>
+      <c r="AS8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr"/>
@@ -1676,6 +1700,8 @@
       <c r="AO9" t="inlineStr"/>
       <c r="AP9" t="inlineStr"/>
       <c r="AQ9" t="inlineStr"/>
+      <c r="AR9" t="inlineStr"/>
+      <c r="AS9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr"/>
@@ -1805,6 +1831,8 @@
       <c r="AO10" t="inlineStr"/>
       <c r="AP10" t="inlineStr"/>
       <c r="AQ10" t="inlineStr"/>
+      <c r="AR10" t="inlineStr"/>
+      <c r="AS10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr"/>
@@ -1934,6 +1962,8 @@
       <c r="AO11" t="inlineStr"/>
       <c r="AP11" t="inlineStr"/>
       <c r="AQ11" t="inlineStr"/>
+      <c r="AR11" t="inlineStr"/>
+      <c r="AS11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr"/>
@@ -2063,6 +2093,8 @@
       <c r="AO12" t="inlineStr"/>
       <c r="AP12" t="inlineStr"/>
       <c r="AQ12" t="inlineStr"/>
+      <c r="AR12" t="inlineStr"/>
+      <c r="AS12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr"/>
@@ -2192,6 +2224,8 @@
       <c r="AO13" t="inlineStr"/>
       <c r="AP13" t="inlineStr"/>
       <c r="AQ13" t="inlineStr"/>
+      <c r="AR13" t="inlineStr"/>
+      <c r="AS13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr"/>
@@ -2321,6 +2355,8 @@
       <c r="AO14" t="inlineStr"/>
       <c r="AP14" t="inlineStr"/>
       <c r="AQ14" t="inlineStr"/>
+      <c r="AR14" t="inlineStr"/>
+      <c r="AS14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr"/>
@@ -2450,6 +2486,8 @@
       <c r="AO15" t="inlineStr"/>
       <c r="AP15" t="inlineStr"/>
       <c r="AQ15" t="inlineStr"/>
+      <c r="AR15" t="inlineStr"/>
+      <c r="AS15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr"/>
@@ -2579,6 +2617,8 @@
       <c r="AO16" t="inlineStr"/>
       <c r="AP16" t="inlineStr"/>
       <c r="AQ16" t="inlineStr"/>
+      <c r="AR16" t="inlineStr"/>
+      <c r="AS16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr"/>
@@ -2708,6 +2748,8 @@
       <c r="AO17" t="inlineStr"/>
       <c r="AP17" t="inlineStr"/>
       <c r="AQ17" t="inlineStr"/>
+      <c r="AR17" t="inlineStr"/>
+      <c r="AS17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr"/>
@@ -2841,6 +2883,8 @@
       <c r="AO18" t="inlineStr"/>
       <c r="AP18" t="inlineStr"/>
       <c r="AQ18" t="inlineStr"/>
+      <c r="AR18" t="inlineStr"/>
+      <c r="AS18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr"/>
@@ -2974,6 +3018,8 @@
       <c r="AO19" t="inlineStr"/>
       <c r="AP19" t="inlineStr"/>
       <c r="AQ19" t="inlineStr"/>
+      <c r="AR19" t="inlineStr"/>
+      <c r="AS19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr"/>
@@ -3107,6 +3153,8 @@
       <c r="AO20" t="inlineStr"/>
       <c r="AP20" t="inlineStr"/>
       <c r="AQ20" t="inlineStr"/>
+      <c r="AR20" t="inlineStr"/>
+      <c r="AS20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr"/>
@@ -3240,6 +3288,147 @@
       <c r="AO21" t="inlineStr"/>
       <c r="AP21" t="inlineStr"/>
       <c r="AQ21" t="inlineStr"/>
+      <c r="AR21" t="inlineStr"/>
+      <c r="AS21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr"/>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>BSND</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>PA_BBND</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>torch.bfloat16</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>torch.float8_e4m3fn</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>torch.float8_e4m3fn</t>
+        </is>
+      </c>
+      <c r="G22" t="n">
+        <v>2</v>
+      </c>
+      <c r="H22" t="n">
+        <v>2</v>
+      </c>
+      <c r="I22" t="n">
+        <v>8192</v>
+      </c>
+      <c r="J22" t="n">
+        <v>128</v>
+      </c>
+      <c r="K22" t="n">
+        <v>1</v>
+      </c>
+      <c r="L22" t="n">
+        <v>512</v>
+      </c>
+      <c r="M22" t="n">
+        <v>256</v>
+      </c>
+      <c r="N22" t="n">
+        <v>128</v>
+      </c>
+      <c r="O22" t="inlineStr"/>
+      <c r="P22" t="inlineStr"/>
+      <c r="Q22" t="n">
+        <v>128</v>
+      </c>
+      <c r="R22" t="n">
+        <v>128</v>
+      </c>
+      <c r="S22" t="n">
+        <v>0.04419417</v>
+      </c>
+      <c r="T22" t="n">
+        <v>4</v>
+      </c>
+      <c r="U22" t="n">
+        <v>0</v>
+      </c>
+      <c r="V22" t="n">
+        <v>0</v>
+      </c>
+      <c r="W22" t="inlineStr"/>
+      <c r="X22" t="inlineStr"/>
+      <c r="Y22" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>64</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>64</v>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>ORI_CMP_SPARSE</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>full</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="inlineStr">
+        <is>
+          <t>fullK</t>
+        </is>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>fullK</t>
+        </is>
+      </c>
+      <c r="AI22" t="inlineStr">
+        <is>
+          <t>full</t>
+        </is>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>full</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>[64, 32, 48, 16]</t>
+        </is>
+      </c>
+      <c r="AL22" t="inlineStr">
+        <is>
+          <t>[32, 16, 24, 8]</t>
+        </is>
+      </c>
+      <c r="AM22" t="inlineStr"/>
+      <c r="AN22" t="inlineStr"/>
+      <c r="AO22" t="inlineStr"/>
+      <c r="AP22" t="inlineStr"/>
+      <c r="AQ22" t="inlineStr"/>
+      <c r="AR22" t="inlineStr"/>
+      <c r="AS22" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
